--- a/resources/report/60/95/ex_04ss/HD_WT_04SS_5.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_WT_04SS_5.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03AEEFB-C678-455C-A0A2-674A75A05766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7020"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -128,8 +129,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,12 +193,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
@@ -346,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -363,7 +358,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -372,56 +367,50 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -430,9 +419,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -457,28 +443,76 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -493,56 +527,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,7 +567,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -872,7 +867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -893,70 +888,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="16"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-      <c r="G5" s="17"/>
+      <c r="G5" s="15"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -964,149 +956,148 @@
     </row>
     <row r="6" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="10.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="20"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1119,418 +1110,394 @@
     </row>
     <row r="17" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="7"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40" t="s">
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39" t="s">
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="7"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40" t="s">
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39" t="s">
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="29" t="s">
+      <c r="C29" s="43"/>
+      <c r="D29" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="30" t="s">
+      <c r="H29" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="62" t="s">
+      <c r="I29" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="63"/>
+      <c r="J29" s="45"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="65"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="47"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="24"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="22"/>
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="24"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="22"/>
       <c r="K33" s="7"/>
     </row>
     <row r="34" spans="1:12" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="55"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
       <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:12" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="57" t="s">
+    <row r="37" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="C37" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="57" t="s">
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="1:12" s="12" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="56" t="s">
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" s="6" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="C38" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="56" t="s">
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="11"/>
-    </row>
-    <row r="39" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="11"/>
-    </row>
-    <row r="40" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="32" t="s">
+      <c r="I38" s="37"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="10"/>
+    </row>
+    <row r="39" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="K39" s="10"/>
+    </row>
+    <row r="40" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="18"/>
-    </row>
-    <row r="41" spans="1:12" s="12" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="53" t="s">
+      <c r="E40" s="28"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="1:12" s="6" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="26"/>
-    </row>
-    <row r="42" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="11"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="23"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="24"/>
+    </row>
+    <row r="42" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="C42" s="10"/>
       <c r="D42" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E42" s="8"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="6"/>
-    </row>
-    <row r="43" spans="1:12" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="10"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="11"/>
-    </row>
-    <row r="44" spans="1:12" s="12" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
+      <c r="F42" s="12"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="1:12" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="1:12" s="6" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -1540,28 +1507,16 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
-      <c r="K44" s="14"/>
+      <c r="K44" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="H25:J25"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="C3:J3"/>
@@ -1578,12 +1533,24 @@
     <mergeCell ref="B13:J13"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0.75" header="0.3" footer="0.3"/>
